--- a/file/gwangmyeong-si-geumcheon-gu.xlsx
+++ b/file/gwangmyeong-si-geumcheon-gu.xlsx
@@ -1,35 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roy\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78DAAC72-1813-4D6F-9177-43F91C4182D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A76AA8BA-B185-4C30-AC52-8ED52420E2CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18960" yWindow="3030" windowWidth="16410" windowHeight="9960" xr2:uid="{4B542028-08CF-49B9-8746-868E717D6C7D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4B542028-08CF-49B9-8746-868E717D6C7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -39,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
   <si>
     <t>두산위브</t>
   </si>
@@ -355,6 +344,19 @@
   </si>
   <si>
     <t>단지명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>철산자이브리에르</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -362,7 +364,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,6 +401,13 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -414,7 +423,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -437,13 +446,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -458,6 +478,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,39 +513,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -571,7 +597,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -682,6 +708,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -690,13 +723,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -761,31 +787,11 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -793,7 +799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED40E87-7CF7-414F-9E97-2A2C6B4DFFF0}">
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="45" customWidth="1"/>
@@ -1655,6 +1661,14 @@
         <v>102</v>
       </c>
     </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="5">
+        <v>163557</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
